--- a/public/reports/histograma-inmuebles-por-tipo-y-anio.xlsx
+++ b/public/reports/histograma-inmuebles-por-tipo-y-anio.xlsx
@@ -8,24 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\webapps\laravel\Arrendaoco\public\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A50E300-0062-4B7F-8C9F-BE7A7A908787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445A5B32-7A47-4D61-800E-ABAD99DB964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Histograma" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Histograma!$A$5</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Histograma!$A$6:$A$14</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Histograma!$B$5</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Histograma!$B$6:$B$14</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Histograma!$C$5</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Histograma!$C$6:$C$14</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Histograma!$D$5</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Histograma!$D$6:$D$14</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Histograma!$B$5</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Histograma!$B$6:$B$14</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Histograma!$C$5</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Histograma!$C$6:$C$14</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Histograma!$D$5</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Histograma!$D$6:$D$14</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Histograma!$A$5</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Histograma!$A$6:$A$14</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Reporte</t>
-  </si>
-  <si>
-    <t>Histograma de inmuebles por tipo y a?o</t>
   </si>
   <si>
     <t>Proyecto</t>
@@ -49,13 +64,13 @@
     <t>Cuarto</t>
   </si>
   <si>
-    <t>Total anual</t>
-  </si>
-  <si>
     <t>Total por tipo</t>
   </si>
   <si>
-    <t>Año</t>
+    <t>Histograma de inmuebles por tipo y año</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -225,38 +240,38 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>17</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>19</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>21</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-79F4-4BCD-B7CF-72707A9B794E}"/>
+              <c16:uniqueId val="{00000000-A210-442E-88A8-0804E965A6C3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -327,10 +342,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>13</c:v>
@@ -358,7 +373,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-79F4-4BCD-B7CF-72707A9B794E}"/>
+              <c16:uniqueId val="{00000001-A210-442E-88A8-0804E965A6C3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -429,140 +444,38 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>23</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>26</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-79F4-4BCD-B7CF-72707A9B794E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Histograma!$E$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total anual</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:numRef>
-              <c:f>Histograma!$A$6:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2025</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2026</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Histograma!$E$6:$E$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>54</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>61</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>77</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-79F4-4BCD-B7CF-72707A9B794E}"/>
+              <c16:uniqueId val="{00000002-A210-442E-88A8-0804E965A6C3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -576,11 +489,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="857243903"/>
-        <c:axId val="857244383"/>
+        <c:axId val="1802888719"/>
+        <c:axId val="1802875279"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="857243903"/>
+        <c:axId val="1802888719"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -623,7 +536,7 @@
             <a:endParaRPr lang="es-MX"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="857244383"/>
+        <c:crossAx val="1802875279"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -631,7 +544,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="857244383"/>
+        <c:axId val="1802875279"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -682,7 +595,7 @@
             <a:endParaRPr lang="es-MX"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="857243903"/>
+        <c:crossAx val="1802888719"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1309,23 +1222,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>434340</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
+        <xdr:cNvPr id="4" name="Gráfico 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD558E83-3216-7C08-0A18-9BCC80CA3C3A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DEAC854-FF91-6659-8850-6B3C3D55F3FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1663,128 +1576,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2018</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2019</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>7</v>
-      </c>
-      <c r="E7">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2020</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8">
-        <v>10</v>
-      </c>
-      <c r="E8">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2021</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>16</v>
       </c>
       <c r="D9">
-        <v>12</v>
-      </c>
-      <c r="E9">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2022</v>
       </c>
       <c r="B10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>18</v>
@@ -1792,81 +1690,66 @@
       <c r="D10">
         <v>15</v>
       </c>
-      <c r="E10">
-        <v>46</v>
-      </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2023</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>21</v>
       </c>
       <c r="D11">
-        <v>18</v>
-      </c>
-      <c r="E11">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2024</v>
       </c>
       <c r="B12">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>24</v>
       </c>
       <c r="D12">
-        <v>20</v>
-      </c>
-      <c r="E12">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2025</v>
       </c>
       <c r="B13">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>27</v>
       </c>
       <c r="D13">
-        <v>23</v>
-      </c>
-      <c r="E13">
-        <v>69</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2026</v>
       </c>
       <c r="B14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C14">
         <v>30</v>
       </c>
       <c r="D14">
-        <v>26</v>
-      </c>
-      <c r="E14">
-        <v>77</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16">
         <v>119</v>
@@ -1876,9 +1759,6 @@
       </c>
       <c r="D16">
         <v>136</v>
-      </c>
-      <c r="E16">
-        <v>424</v>
       </c>
     </row>
   </sheetData>
